--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.21.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.21.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.21.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.21.xlsx
@@ -422,16 +422,16 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -607,18 +607,18 @@
           <t>L52: line starts with digit/letter garbage token | suspicious token(s): 1judgment (letter/digit mix) | localized OCR phrase divergence vs other OCR: "" vs "1judgment" :: 1judgment, under which such subsequent purchaser, mort-</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>L153: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œtha</t>
-        </is>
-      </c>
+      <c r="J2" s="1" t="inlineStr"/>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L7: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: ment, or at any time afterwards, be seized, possessed orâ€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]N</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]N</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 14</t>
@@ -626,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L5: symbol-only separator/garbage line :: 14 -</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]N</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>94</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -677,7 +677,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L32: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€ž. , icates. Provided nevertheless, that nothing therein</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: ment, or at any time afterwards, be seized, possessed or•</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -689,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line | punctuation artifact: repeated periods :: 7..</t>
+          <t>L5: symbol-only separator/garbage line :: 14 -</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -736,7 +736,7 @@
       <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L56: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: gageeâ€˜</t>
+          <t>L108: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -748,7 +748,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 8.</t>
+          <t>L79: isolated marker/symbol line | punctuation artifact: repeated periods :: 7..</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -774,12 +774,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -789,11 +789,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -803,7 +799,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 9.</t>
+          <t>L84: isolated marker/symbol line :: 8.</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -850,7 +846,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L91: isolated marker/symbol line :: 9.</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -897,7 +893,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L110: isolated marker/symbol line :: /</t>
+          <t>L108: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -942,7 +938,11 @@
           <t>L126: isolated marker/symbol line :: 9.</t>
         </is>
       </c>
-      <c r="O8" s="1" t="inlineStr"/>
+      <c r="O8" s="1" t="inlineStr">
+        <is>
+          <t>L110: isolated marker/symbol line :: /</t>
+        </is>
+      </c>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
